--- a/employment_forms/026_employment_history_release_form--employment_forms.xlsx
+++ b/employment_forms/026_employment_history_release_form--employment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -880,7 +880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>coo</t>
+          <t>clo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>COO</t>
+          <t>CLO</t>
         </is>
       </c>
     </row>
@@ -1049,46 +1049,46 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>clo</t>
+          <t>director</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLO</t>
+          <t>Director</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_titles_choices</t>
+          <t>job_locations_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>cfo</t>
+          <t>san_francisco</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CFO</t>
+          <t>San Francisco</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_titles_choices</t>
+          <t>job_locations_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>director</t>
+          <t>new_york</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Director</t>
+          <t>New York</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>san_francisco</t>
+          <t>london</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>London</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>new_york</t>
+          <t>paris</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Paris</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>london</t>
+          <t>tokyo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Tokyo</t>
         </is>
       </c>
     </row>
@@ -1151,46 +1151,46 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>paris</t>
+          <t>munich</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Munich</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_locations_choices</t>
+          <t>employment_status_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>tokyo</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_locations_choices</t>
+          <t>employment_status_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>munich</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Unemployed</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>employed</t>
+          <t>employed_-_not_seeking</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Employed</t>
+          <t>Employed - Not Seeking</t>
         </is>
       </c>
     </row>
@@ -1219,46 +1219,46 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>unemployed</t>
+          <t>retired</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Unemployed</t>
+          <t>Retired</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>employment_status_choices</t>
+          <t>employment_type_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>employed_-_not_seeking</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Employed - Not Seeking</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>employment_status_choices</t>
+          <t>employment_type_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>retired</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Retired</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
@@ -1270,78 +1270,44 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>full-time</t>
+          <t>freelance</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Freelance</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>employment_type_choices</t>
+          <t>benefits_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>part-time</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Part-time</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>employment_type_choices</t>
+          <t>benefits_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>freelance</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
-        <is>
-          <t>Freelance</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>benefits_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>benefits_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
         <is>
           <t>No</t>
         </is>
